--- a/public/templates/sailing-school-staff-rota-template.xlsx
+++ b/public/templates/sailing-school-staff-rota-template.xlsx
@@ -561,14 +561,14 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   'Instructors needed' works it out; fill the Senior and Safety boat columns first, then instructors and assistants.</t>
+          <t xml:space="preserve">   'Instructors needed' works it out; fill the Senior Instructor column first, then instructors and assistants. The instructors drive the safety boats.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   'Check' flags sessions that are short of instructors or have no safety boat driver. Fix those before you share the rota.</t>
+          <t xml:space="preserve">   'Check' flags sessions that are short of instructors or have no Senior Instructor on. Fix those before you share the rota.</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="J1" s="5" t="inlineStr">
         <is>
-          <t>Safety boat ticket expiry</t>
+          <t>Powerboat / safety boat ticket expiry</t>
         </is>
       </c>
       <c r="K1" s="5" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Safety boat driver</t>
+          <t>Powerboat Instructor</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -871,8 +871,14 @@
           <t>07700 900004</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Powerboat Instructor</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>47150</v>
+      </c>
       <c r="G5" s="7" t="n">
         <v>46569</v>
       </c>
@@ -3371,7 +3377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3385,10 +3391,9 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3449,20 +3454,15 @@
       </c>
       <c r="L1" s="5" t="inlineStr">
         <is>
-          <t>Safety boat driver</t>
+          <t>Safety boat</t>
         </is>
       </c>
       <c r="M1" s="5" t="inlineStr">
         <is>
-          <t>Safety boat</t>
+          <t>Instructors rostered</t>
         </is>
       </c>
       <c r="N1" s="5" t="inlineStr">
-        <is>
-          <t>Instructors rostered</t>
-        </is>
-      </c>
-      <c r="O1" s="5" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
@@ -3486,7 +3486,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" s="6">
         <f>IF(OR(D2="",E2=""),"",ROUNDUP(D2/E2,0))</f>
@@ -3511,20 +3511,15 @@
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>Chris Lee</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
           <t>Safety boat 1</t>
         </is>
       </c>
+      <c r="M2" s="6">
+        <f>IF(C2="","",COUNTA(G2:J2))</f>
+        <v/>
+      </c>
       <c r="N2" s="6">
-        <f>IF(C2="","",COUNTA(G2:J2))</f>
-        <v/>
-      </c>
-      <c r="O2" s="6">
-        <f>IF(C2="","",IF(N2&lt;F2,"SHORT by "&amp;(F2-N2),"")&amp;IF(L2="",IF(N2&lt;F2," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C2="","",IF(M2&lt;F2,"SHORT by "&amp;(F2-M2),"")&amp;IF(G2="",IF(M2&lt;F2," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3546,17 +3541,13 @@
         <v>6</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F3" s="6">
         <f>IF(OR(D3="",E3=""),"",ROUNDUP(D3/E3,0))</f>
         <v/>
       </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Alex Jones</t>
-        </is>
-      </c>
+      <c r="G3" s="6" t="n"/>
       <c r="H3" s="6" t="inlineStr">
         <is>
           <t>Sam Patel</t>
@@ -3565,14 +3556,17 @@
       <c r="I3" s="6" t="n"/>
       <c r="J3" s="6" t="n"/>
       <c r="K3" s="6" t="n"/>
-      <c r="L3" s="6" t="n"/>
-      <c r="M3" s="6" t="n"/>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Safety boat 1</t>
+        </is>
+      </c>
+      <c r="M3" s="6">
+        <f>IF(C3="","",COUNTA(G3:J3))</f>
+        <v/>
+      </c>
       <c r="N3" s="6">
-        <f>IF(C3="","",COUNTA(G3:J3))</f>
-        <v/>
-      </c>
-      <c r="O3" s="6">
-        <f>IF(C3="","",IF(N3&lt;F3,"SHORT by "&amp;(F3-N3),"")&amp;IF(L3="",IF(N3&lt;F3," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C3="","",IF(M3&lt;F3,"SHORT by "&amp;(F3-M3),"")&amp;IF(G3="",IF(M3&lt;F3," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3592,13 +3586,12 @@
       <c r="J4" s="6" t="n"/>
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
-      <c r="M4" s="6" t="n"/>
+      <c r="M4" s="6">
+        <f>IF(C4="","",COUNTA(G4:J4))</f>
+        <v/>
+      </c>
       <c r="N4" s="6">
-        <f>IF(C4="","",COUNTA(G4:J4))</f>
-        <v/>
-      </c>
-      <c r="O4" s="6">
-        <f>IF(C4="","",IF(N4&lt;F4,"SHORT by "&amp;(F4-N4),"")&amp;IF(L4="",IF(N4&lt;F4," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C4="","",IF(M4&lt;F4,"SHORT by "&amp;(F4-M4),"")&amp;IF(G4="",IF(M4&lt;F4," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3618,13 +3611,12 @@
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="L5" s="6" t="n"/>
-      <c r="M5" s="6" t="n"/>
+      <c r="M5" s="6">
+        <f>IF(C5="","",COUNTA(G5:J5))</f>
+        <v/>
+      </c>
       <c r="N5" s="6">
-        <f>IF(C5="","",COUNTA(G5:J5))</f>
-        <v/>
-      </c>
-      <c r="O5" s="6">
-        <f>IF(C5="","",IF(N5&lt;F5,"SHORT by "&amp;(F5-N5),"")&amp;IF(L5="",IF(N5&lt;F5," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C5="","",IF(M5&lt;F5,"SHORT by "&amp;(F5-M5),"")&amp;IF(G5="",IF(M5&lt;F5," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3644,13 +3636,12 @@
       <c r="J6" s="6" t="n"/>
       <c r="K6" s="6" t="n"/>
       <c r="L6" s="6" t="n"/>
-      <c r="M6" s="6" t="n"/>
+      <c r="M6" s="6">
+        <f>IF(C6="","",COUNTA(G6:J6))</f>
+        <v/>
+      </c>
       <c r="N6" s="6">
-        <f>IF(C6="","",COUNTA(G6:J6))</f>
-        <v/>
-      </c>
-      <c r="O6" s="6">
-        <f>IF(C6="","",IF(N6&lt;F6,"SHORT by "&amp;(F6-N6),"")&amp;IF(L6="",IF(N6&lt;F6," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C6="","",IF(M6&lt;F6,"SHORT by "&amp;(F6-M6),"")&amp;IF(G6="",IF(M6&lt;F6," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3670,13 +3661,12 @@
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="6" t="n"/>
       <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
+      <c r="M7" s="6">
+        <f>IF(C7="","",COUNTA(G7:J7))</f>
+        <v/>
+      </c>
       <c r="N7" s="6">
-        <f>IF(C7="","",COUNTA(G7:J7))</f>
-        <v/>
-      </c>
-      <c r="O7" s="6">
-        <f>IF(C7="","",IF(N7&lt;F7,"SHORT by "&amp;(F7-N7),"")&amp;IF(L7="",IF(N7&lt;F7," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C7="","",IF(M7&lt;F7,"SHORT by "&amp;(F7-M7),"")&amp;IF(G7="",IF(M7&lt;F7," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3696,13 +3686,12 @@
       <c r="J8" s="6" t="n"/>
       <c r="K8" s="6" t="n"/>
       <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
+      <c r="M8" s="6">
+        <f>IF(C8="","",COUNTA(G8:J8))</f>
+        <v/>
+      </c>
       <c r="N8" s="6">
-        <f>IF(C8="","",COUNTA(G8:J8))</f>
-        <v/>
-      </c>
-      <c r="O8" s="6">
-        <f>IF(C8="","",IF(N8&lt;F8,"SHORT by "&amp;(F8-N8),"")&amp;IF(L8="",IF(N8&lt;F8," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C8="","",IF(M8&lt;F8,"SHORT by "&amp;(F8-M8),"")&amp;IF(G8="",IF(M8&lt;F8," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3722,13 +3711,12 @@
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="6" t="n"/>
       <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
+      <c r="M9" s="6">
+        <f>IF(C9="","",COUNTA(G9:J9))</f>
+        <v/>
+      </c>
       <c r="N9" s="6">
-        <f>IF(C9="","",COUNTA(G9:J9))</f>
-        <v/>
-      </c>
-      <c r="O9" s="6">
-        <f>IF(C9="","",IF(N9&lt;F9,"SHORT by "&amp;(F9-N9),"")&amp;IF(L9="",IF(N9&lt;F9," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C9="","",IF(M9&lt;F9,"SHORT by "&amp;(F9-M9),"")&amp;IF(G9="",IF(M9&lt;F9," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3748,13 +3736,12 @@
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
       <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
+      <c r="M10" s="6">
+        <f>IF(C10="","",COUNTA(G10:J10))</f>
+        <v/>
+      </c>
       <c r="N10" s="6">
-        <f>IF(C10="","",COUNTA(G10:J10))</f>
-        <v/>
-      </c>
-      <c r="O10" s="6">
-        <f>IF(C10="","",IF(N10&lt;F10,"SHORT by "&amp;(F10-N10),"")&amp;IF(L10="",IF(N10&lt;F10," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C10="","",IF(M10&lt;F10,"SHORT by "&amp;(F10-M10),"")&amp;IF(G10="",IF(M10&lt;F10," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3774,13 +3761,12 @@
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="6" t="n"/>
       <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
+      <c r="M11" s="6">
+        <f>IF(C11="","",COUNTA(G11:J11))</f>
+        <v/>
+      </c>
       <c r="N11" s="6">
-        <f>IF(C11="","",COUNTA(G11:J11))</f>
-        <v/>
-      </c>
-      <c r="O11" s="6">
-        <f>IF(C11="","",IF(N11&lt;F11,"SHORT by "&amp;(F11-N11),"")&amp;IF(L11="",IF(N11&lt;F11," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C11="","",IF(M11&lt;F11,"SHORT by "&amp;(F11-M11),"")&amp;IF(G11="",IF(M11&lt;F11," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3800,13 +3786,12 @@
       <c r="J12" s="6" t="n"/>
       <c r="K12" s="6" t="n"/>
       <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
+      <c r="M12" s="6">
+        <f>IF(C12="","",COUNTA(G12:J12))</f>
+        <v/>
+      </c>
       <c r="N12" s="6">
-        <f>IF(C12="","",COUNTA(G12:J12))</f>
-        <v/>
-      </c>
-      <c r="O12" s="6">
-        <f>IF(C12="","",IF(N12&lt;F12,"SHORT by "&amp;(F12-N12),"")&amp;IF(L12="",IF(N12&lt;F12," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C12="","",IF(M12&lt;F12,"SHORT by "&amp;(F12-M12),"")&amp;IF(G12="",IF(M12&lt;F12," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3826,13 +3811,12 @@
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
       <c r="L13" s="6" t="n"/>
-      <c r="M13" s="6" t="n"/>
+      <c r="M13" s="6">
+        <f>IF(C13="","",COUNTA(G13:J13))</f>
+        <v/>
+      </c>
       <c r="N13" s="6">
-        <f>IF(C13="","",COUNTA(G13:J13))</f>
-        <v/>
-      </c>
-      <c r="O13" s="6">
-        <f>IF(C13="","",IF(N13&lt;F13,"SHORT by "&amp;(F13-N13),"")&amp;IF(L13="",IF(N13&lt;F13," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C13="","",IF(M13&lt;F13,"SHORT by "&amp;(F13-M13),"")&amp;IF(G13="",IF(M13&lt;F13," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3852,13 +3836,12 @@
       <c r="J14" s="6" t="n"/>
       <c r="K14" s="6" t="n"/>
       <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
+      <c r="M14" s="6">
+        <f>IF(C14="","",COUNTA(G14:J14))</f>
+        <v/>
+      </c>
       <c r="N14" s="6">
-        <f>IF(C14="","",COUNTA(G14:J14))</f>
-        <v/>
-      </c>
-      <c r="O14" s="6">
-        <f>IF(C14="","",IF(N14&lt;F14,"SHORT by "&amp;(F14-N14),"")&amp;IF(L14="",IF(N14&lt;F14," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C14="","",IF(M14&lt;F14,"SHORT by "&amp;(F14-M14),"")&amp;IF(G14="",IF(M14&lt;F14," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3878,13 +3861,12 @@
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="6" t="n"/>
       <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
+      <c r="M15" s="6">
+        <f>IF(C15="","",COUNTA(G15:J15))</f>
+        <v/>
+      </c>
       <c r="N15" s="6">
-        <f>IF(C15="","",COUNTA(G15:J15))</f>
-        <v/>
-      </c>
-      <c r="O15" s="6">
-        <f>IF(C15="","",IF(N15&lt;F15,"SHORT by "&amp;(F15-N15),"")&amp;IF(L15="",IF(N15&lt;F15," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C15="","",IF(M15&lt;F15,"SHORT by "&amp;(F15-M15),"")&amp;IF(G15="",IF(M15&lt;F15," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3904,13 +3886,12 @@
       <c r="J16" s="6" t="n"/>
       <c r="K16" s="6" t="n"/>
       <c r="L16" s="6" t="n"/>
-      <c r="M16" s="6" t="n"/>
+      <c r="M16" s="6">
+        <f>IF(C16="","",COUNTA(G16:J16))</f>
+        <v/>
+      </c>
       <c r="N16" s="6">
-        <f>IF(C16="","",COUNTA(G16:J16))</f>
-        <v/>
-      </c>
-      <c r="O16" s="6">
-        <f>IF(C16="","",IF(N16&lt;F16,"SHORT by "&amp;(F16-N16),"")&amp;IF(L16="",IF(N16&lt;F16," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C16="","",IF(M16&lt;F16,"SHORT by "&amp;(F16-M16),"")&amp;IF(G16="",IF(M16&lt;F16," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3930,13 +3911,12 @@
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="6" t="n"/>
       <c r="L17" s="6" t="n"/>
-      <c r="M17" s="6" t="n"/>
+      <c r="M17" s="6">
+        <f>IF(C17="","",COUNTA(G17:J17))</f>
+        <v/>
+      </c>
       <c r="N17" s="6">
-        <f>IF(C17="","",COUNTA(G17:J17))</f>
-        <v/>
-      </c>
-      <c r="O17" s="6">
-        <f>IF(C17="","",IF(N17&lt;F17,"SHORT by "&amp;(F17-N17),"")&amp;IF(L17="",IF(N17&lt;F17," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C17="","",IF(M17&lt;F17,"SHORT by "&amp;(F17-M17),"")&amp;IF(G17="",IF(M17&lt;F17," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3956,13 +3936,12 @@
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="6" t="n"/>
       <c r="L18" s="6" t="n"/>
-      <c r="M18" s="6" t="n"/>
+      <c r="M18" s="6">
+        <f>IF(C18="","",COUNTA(G18:J18))</f>
+        <v/>
+      </c>
       <c r="N18" s="6">
-        <f>IF(C18="","",COUNTA(G18:J18))</f>
-        <v/>
-      </c>
-      <c r="O18" s="6">
-        <f>IF(C18="","",IF(N18&lt;F18,"SHORT by "&amp;(F18-N18),"")&amp;IF(L18="",IF(N18&lt;F18," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C18="","",IF(M18&lt;F18,"SHORT by "&amp;(F18-M18),"")&amp;IF(G18="",IF(M18&lt;F18," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -3982,13 +3961,12 @@
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="6" t="n"/>
       <c r="L19" s="6" t="n"/>
-      <c r="M19" s="6" t="n"/>
+      <c r="M19" s="6">
+        <f>IF(C19="","",COUNTA(G19:J19))</f>
+        <v/>
+      </c>
       <c r="N19" s="6">
-        <f>IF(C19="","",COUNTA(G19:J19))</f>
-        <v/>
-      </c>
-      <c r="O19" s="6">
-        <f>IF(C19="","",IF(N19&lt;F19,"SHORT by "&amp;(F19-N19),"")&amp;IF(L19="",IF(N19&lt;F19," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C19="","",IF(M19&lt;F19,"SHORT by "&amp;(F19-M19),"")&amp;IF(G19="",IF(M19&lt;F19," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4008,13 +3986,12 @@
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="6" t="n"/>
       <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6" t="n"/>
+      <c r="M20" s="6">
+        <f>IF(C20="","",COUNTA(G20:J20))</f>
+        <v/>
+      </c>
       <c r="N20" s="6">
-        <f>IF(C20="","",COUNTA(G20:J20))</f>
-        <v/>
-      </c>
-      <c r="O20" s="6">
-        <f>IF(C20="","",IF(N20&lt;F20,"SHORT by "&amp;(F20-N20),"")&amp;IF(L20="",IF(N20&lt;F20," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C20="","",IF(M20&lt;F20,"SHORT by "&amp;(F20-M20),"")&amp;IF(G20="",IF(M20&lt;F20," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4034,13 +4011,12 @@
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="n"/>
       <c r="L21" s="6" t="n"/>
-      <c r="M21" s="6" t="n"/>
+      <c r="M21" s="6">
+        <f>IF(C21="","",COUNTA(G21:J21))</f>
+        <v/>
+      </c>
       <c r="N21" s="6">
-        <f>IF(C21="","",COUNTA(G21:J21))</f>
-        <v/>
-      </c>
-      <c r="O21" s="6">
-        <f>IF(C21="","",IF(N21&lt;F21,"SHORT by "&amp;(F21-N21),"")&amp;IF(L21="",IF(N21&lt;F21," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C21="","",IF(M21&lt;F21,"SHORT by "&amp;(F21-M21),"")&amp;IF(G21="",IF(M21&lt;F21," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4060,13 +4036,12 @@
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="n"/>
       <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
+      <c r="M22" s="6">
+        <f>IF(C22="","",COUNTA(G22:J22))</f>
+        <v/>
+      </c>
       <c r="N22" s="6">
-        <f>IF(C22="","",COUNTA(G22:J22))</f>
-        <v/>
-      </c>
-      <c r="O22" s="6">
-        <f>IF(C22="","",IF(N22&lt;F22,"SHORT by "&amp;(F22-N22),"")&amp;IF(L22="",IF(N22&lt;F22," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C22="","",IF(M22&lt;F22,"SHORT by "&amp;(F22-M22),"")&amp;IF(G22="",IF(M22&lt;F22," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4086,13 +4061,12 @@
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="L23" s="6" t="n"/>
-      <c r="M23" s="6" t="n"/>
+      <c r="M23" s="6">
+        <f>IF(C23="","",COUNTA(G23:J23))</f>
+        <v/>
+      </c>
       <c r="N23" s="6">
-        <f>IF(C23="","",COUNTA(G23:J23))</f>
-        <v/>
-      </c>
-      <c r="O23" s="6">
-        <f>IF(C23="","",IF(N23&lt;F23,"SHORT by "&amp;(F23-N23),"")&amp;IF(L23="",IF(N23&lt;F23," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C23="","",IF(M23&lt;F23,"SHORT by "&amp;(F23-M23),"")&amp;IF(G23="",IF(M23&lt;F23," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4112,13 +4086,12 @@
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="n"/>
       <c r="L24" s="6" t="n"/>
-      <c r="M24" s="6" t="n"/>
+      <c r="M24" s="6">
+        <f>IF(C24="","",COUNTA(G24:J24))</f>
+        <v/>
+      </c>
       <c r="N24" s="6">
-        <f>IF(C24="","",COUNTA(G24:J24))</f>
-        <v/>
-      </c>
-      <c r="O24" s="6">
-        <f>IF(C24="","",IF(N24&lt;F24,"SHORT by "&amp;(F24-N24),"")&amp;IF(L24="",IF(N24&lt;F24," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C24="","",IF(M24&lt;F24,"SHORT by "&amp;(F24-M24),"")&amp;IF(G24="",IF(M24&lt;F24," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4138,13 +4111,12 @@
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="n"/>
       <c r="L25" s="6" t="n"/>
-      <c r="M25" s="6" t="n"/>
+      <c r="M25" s="6">
+        <f>IF(C25="","",COUNTA(G25:J25))</f>
+        <v/>
+      </c>
       <c r="N25" s="6">
-        <f>IF(C25="","",COUNTA(G25:J25))</f>
-        <v/>
-      </c>
-      <c r="O25" s="6">
-        <f>IF(C25="","",IF(N25&lt;F25,"SHORT by "&amp;(F25-N25),"")&amp;IF(L25="",IF(N25&lt;F25," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C25="","",IF(M25&lt;F25,"SHORT by "&amp;(F25-M25),"")&amp;IF(G25="",IF(M25&lt;F25," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4164,13 +4136,12 @@
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="n"/>
       <c r="L26" s="6" t="n"/>
-      <c r="M26" s="6" t="n"/>
+      <c r="M26" s="6">
+        <f>IF(C26="","",COUNTA(G26:J26))</f>
+        <v/>
+      </c>
       <c r="N26" s="6">
-        <f>IF(C26="","",COUNTA(G26:J26))</f>
-        <v/>
-      </c>
-      <c r="O26" s="6">
-        <f>IF(C26="","",IF(N26&lt;F26,"SHORT by "&amp;(F26-N26),"")&amp;IF(L26="",IF(N26&lt;F26," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C26="","",IF(M26&lt;F26,"SHORT by "&amp;(F26-M26),"")&amp;IF(G26="",IF(M26&lt;F26," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4190,13 +4161,12 @@
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="n"/>
       <c r="L27" s="6" t="n"/>
-      <c r="M27" s="6" t="n"/>
+      <c r="M27" s="6">
+        <f>IF(C27="","",COUNTA(G27:J27))</f>
+        <v/>
+      </c>
       <c r="N27" s="6">
-        <f>IF(C27="","",COUNTA(G27:J27))</f>
-        <v/>
-      </c>
-      <c r="O27" s="6">
-        <f>IF(C27="","",IF(N27&lt;F27,"SHORT by "&amp;(F27-N27),"")&amp;IF(L27="",IF(N27&lt;F27," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C27="","",IF(M27&lt;F27,"SHORT by "&amp;(F27-M27),"")&amp;IF(G27="",IF(M27&lt;F27," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4216,13 +4186,12 @@
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="n"/>
       <c r="L28" s="6" t="n"/>
-      <c r="M28" s="6" t="n"/>
+      <c r="M28" s="6">
+        <f>IF(C28="","",COUNTA(G28:J28))</f>
+        <v/>
+      </c>
       <c r="N28" s="6">
-        <f>IF(C28="","",COUNTA(G28:J28))</f>
-        <v/>
-      </c>
-      <c r="O28" s="6">
-        <f>IF(C28="","",IF(N28&lt;F28,"SHORT by "&amp;(F28-N28),"")&amp;IF(L28="",IF(N28&lt;F28," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C28="","",IF(M28&lt;F28,"SHORT by "&amp;(F28-M28),"")&amp;IF(G28="",IF(M28&lt;F28," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4242,13 +4211,12 @@
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="n"/>
       <c r="L29" s="6" t="n"/>
-      <c r="M29" s="6" t="n"/>
+      <c r="M29" s="6">
+        <f>IF(C29="","",COUNTA(G29:J29))</f>
+        <v/>
+      </c>
       <c r="N29" s="6">
-        <f>IF(C29="","",COUNTA(G29:J29))</f>
-        <v/>
-      </c>
-      <c r="O29" s="6">
-        <f>IF(C29="","",IF(N29&lt;F29,"SHORT by "&amp;(F29-N29),"")&amp;IF(L29="",IF(N29&lt;F29," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C29="","",IF(M29&lt;F29,"SHORT by "&amp;(F29-M29),"")&amp;IF(G29="",IF(M29&lt;F29," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4268,13 +4236,12 @@
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="n"/>
       <c r="L30" s="6" t="n"/>
-      <c r="M30" s="6" t="n"/>
+      <c r="M30" s="6">
+        <f>IF(C30="","",COUNTA(G30:J30))</f>
+        <v/>
+      </c>
       <c r="N30" s="6">
-        <f>IF(C30="","",COUNTA(G30:J30))</f>
-        <v/>
-      </c>
-      <c r="O30" s="6">
-        <f>IF(C30="","",IF(N30&lt;F30,"SHORT by "&amp;(F30-N30),"")&amp;IF(L30="",IF(N30&lt;F30," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C30="","",IF(M30&lt;F30,"SHORT by "&amp;(F30-M30),"")&amp;IF(G30="",IF(M30&lt;F30," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4294,13 +4261,12 @@
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="n"/>
       <c r="L31" s="6" t="n"/>
-      <c r="M31" s="6" t="n"/>
+      <c r="M31" s="6">
+        <f>IF(C31="","",COUNTA(G31:J31))</f>
+        <v/>
+      </c>
       <c r="N31" s="6">
-        <f>IF(C31="","",COUNTA(G31:J31))</f>
-        <v/>
-      </c>
-      <c r="O31" s="6">
-        <f>IF(C31="","",IF(N31&lt;F31,"SHORT by "&amp;(F31-N31),"")&amp;IF(L31="",IF(N31&lt;F31," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C31="","",IF(M31&lt;F31,"SHORT by "&amp;(F31-M31),"")&amp;IF(G31="",IF(M31&lt;F31," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4320,13 +4286,12 @@
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="n"/>
       <c r="L32" s="6" t="n"/>
-      <c r="M32" s="6" t="n"/>
+      <c r="M32" s="6">
+        <f>IF(C32="","",COUNTA(G32:J32))</f>
+        <v/>
+      </c>
       <c r="N32" s="6">
-        <f>IF(C32="","",COUNTA(G32:J32))</f>
-        <v/>
-      </c>
-      <c r="O32" s="6">
-        <f>IF(C32="","",IF(N32&lt;F32,"SHORT by "&amp;(F32-N32),"")&amp;IF(L32="",IF(N32&lt;F32," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C32="","",IF(M32&lt;F32,"SHORT by "&amp;(F32-M32),"")&amp;IF(G32="",IF(M32&lt;F32," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4346,13 +4311,12 @@
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="n"/>
       <c r="L33" s="6" t="n"/>
-      <c r="M33" s="6" t="n"/>
+      <c r="M33" s="6">
+        <f>IF(C33="","",COUNTA(G33:J33))</f>
+        <v/>
+      </c>
       <c r="N33" s="6">
-        <f>IF(C33="","",COUNTA(G33:J33))</f>
-        <v/>
-      </c>
-      <c r="O33" s="6">
-        <f>IF(C33="","",IF(N33&lt;F33,"SHORT by "&amp;(F33-N33),"")&amp;IF(L33="",IF(N33&lt;F33," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C33="","",IF(M33&lt;F33,"SHORT by "&amp;(F33-M33),"")&amp;IF(G33="",IF(M33&lt;F33," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4372,13 +4336,12 @@
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="n"/>
       <c r="L34" s="6" t="n"/>
-      <c r="M34" s="6" t="n"/>
+      <c r="M34" s="6">
+        <f>IF(C34="","",COUNTA(G34:J34))</f>
+        <v/>
+      </c>
       <c r="N34" s="6">
-        <f>IF(C34="","",COUNTA(G34:J34))</f>
-        <v/>
-      </c>
-      <c r="O34" s="6">
-        <f>IF(C34="","",IF(N34&lt;F34,"SHORT by "&amp;(F34-N34),"")&amp;IF(L34="",IF(N34&lt;F34," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C34="","",IF(M34&lt;F34,"SHORT by "&amp;(F34-M34),"")&amp;IF(G34="",IF(M34&lt;F34," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4398,13 +4361,12 @@
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="6" t="n"/>
       <c r="L35" s="6" t="n"/>
-      <c r="M35" s="6" t="n"/>
+      <c r="M35" s="6">
+        <f>IF(C35="","",COUNTA(G35:J35))</f>
+        <v/>
+      </c>
       <c r="N35" s="6">
-        <f>IF(C35="","",COUNTA(G35:J35))</f>
-        <v/>
-      </c>
-      <c r="O35" s="6">
-        <f>IF(C35="","",IF(N35&lt;F35,"SHORT by "&amp;(F35-N35),"")&amp;IF(L35="",IF(N35&lt;F35," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C35="","",IF(M35&lt;F35,"SHORT by "&amp;(F35-M35),"")&amp;IF(G35="",IF(M35&lt;F35," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4424,13 +4386,12 @@
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="n"/>
       <c r="L36" s="6" t="n"/>
-      <c r="M36" s="6" t="n"/>
+      <c r="M36" s="6">
+        <f>IF(C36="","",COUNTA(G36:J36))</f>
+        <v/>
+      </c>
       <c r="N36" s="6">
-        <f>IF(C36="","",COUNTA(G36:J36))</f>
-        <v/>
-      </c>
-      <c r="O36" s="6">
-        <f>IF(C36="","",IF(N36&lt;F36,"SHORT by "&amp;(F36-N36),"")&amp;IF(L36="",IF(N36&lt;F36," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C36="","",IF(M36&lt;F36,"SHORT by "&amp;(F36-M36),"")&amp;IF(G36="",IF(M36&lt;F36," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4450,13 +4411,12 @@
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="6" t="n"/>
       <c r="L37" s="6" t="n"/>
-      <c r="M37" s="6" t="n"/>
+      <c r="M37" s="6">
+        <f>IF(C37="","",COUNTA(G37:J37))</f>
+        <v/>
+      </c>
       <c r="N37" s="6">
-        <f>IF(C37="","",COUNTA(G37:J37))</f>
-        <v/>
-      </c>
-      <c r="O37" s="6">
-        <f>IF(C37="","",IF(N37&lt;F37,"SHORT by "&amp;(F37-N37),"")&amp;IF(L37="",IF(N37&lt;F37," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C37="","",IF(M37&lt;F37,"SHORT by "&amp;(F37-M37),"")&amp;IF(G37="",IF(M37&lt;F37," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4476,13 +4436,12 @@
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="6" t="n"/>
       <c r="L38" s="6" t="n"/>
-      <c r="M38" s="6" t="n"/>
+      <c r="M38" s="6">
+        <f>IF(C38="","",COUNTA(G38:J38))</f>
+        <v/>
+      </c>
       <c r="N38" s="6">
-        <f>IF(C38="","",COUNTA(G38:J38))</f>
-        <v/>
-      </c>
-      <c r="O38" s="6">
-        <f>IF(C38="","",IF(N38&lt;F38,"SHORT by "&amp;(F38-N38),"")&amp;IF(L38="",IF(N38&lt;F38," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C38="","",IF(M38&lt;F38,"SHORT by "&amp;(F38-M38),"")&amp;IF(G38="",IF(M38&lt;F38," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4502,13 +4461,12 @@
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="n"/>
       <c r="L39" s="6" t="n"/>
-      <c r="M39" s="6" t="n"/>
+      <c r="M39" s="6">
+        <f>IF(C39="","",COUNTA(G39:J39))</f>
+        <v/>
+      </c>
       <c r="N39" s="6">
-        <f>IF(C39="","",COUNTA(G39:J39))</f>
-        <v/>
-      </c>
-      <c r="O39" s="6">
-        <f>IF(C39="","",IF(N39&lt;F39,"SHORT by "&amp;(F39-N39),"")&amp;IF(L39="",IF(N39&lt;F39," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C39="","",IF(M39&lt;F39,"SHORT by "&amp;(F39-M39),"")&amp;IF(G39="",IF(M39&lt;F39," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4528,13 +4486,12 @@
       <c r="J40" s="6" t="n"/>
       <c r="K40" s="6" t="n"/>
       <c r="L40" s="6" t="n"/>
-      <c r="M40" s="6" t="n"/>
+      <c r="M40" s="6">
+        <f>IF(C40="","",COUNTA(G40:J40))</f>
+        <v/>
+      </c>
       <c r="N40" s="6">
-        <f>IF(C40="","",COUNTA(G40:J40))</f>
-        <v/>
-      </c>
-      <c r="O40" s="6">
-        <f>IF(C40="","",IF(N40&lt;F40,"SHORT by "&amp;(F40-N40),"")&amp;IF(L40="",IF(N40&lt;F40," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C40="","",IF(M40&lt;F40,"SHORT by "&amp;(F40-M40),"")&amp;IF(G40="",IF(M40&lt;F40," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4554,13 +4511,12 @@
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="6" t="n"/>
       <c r="L41" s="6" t="n"/>
-      <c r="M41" s="6" t="n"/>
+      <c r="M41" s="6">
+        <f>IF(C41="","",COUNTA(G41:J41))</f>
+        <v/>
+      </c>
       <c r="N41" s="6">
-        <f>IF(C41="","",COUNTA(G41:J41))</f>
-        <v/>
-      </c>
-      <c r="O41" s="6">
-        <f>IF(C41="","",IF(N41&lt;F41,"SHORT by "&amp;(F41-N41),"")&amp;IF(L41="",IF(N41&lt;F41," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C41="","",IF(M41&lt;F41,"SHORT by "&amp;(F41-M41),"")&amp;IF(G41="",IF(M41&lt;F41," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4580,13 +4536,12 @@
       <c r="J42" s="6" t="n"/>
       <c r="K42" s="6" t="n"/>
       <c r="L42" s="6" t="n"/>
-      <c r="M42" s="6" t="n"/>
+      <c r="M42" s="6">
+        <f>IF(C42="","",COUNTA(G42:J42))</f>
+        <v/>
+      </c>
       <c r="N42" s="6">
-        <f>IF(C42="","",COUNTA(G42:J42))</f>
-        <v/>
-      </c>
-      <c r="O42" s="6">
-        <f>IF(C42="","",IF(N42&lt;F42,"SHORT by "&amp;(F42-N42),"")&amp;IF(L42="",IF(N42&lt;F42," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C42="","",IF(M42&lt;F42,"SHORT by "&amp;(F42-M42),"")&amp;IF(G42="",IF(M42&lt;F42," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4606,13 +4561,12 @@
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="6" t="n"/>
       <c r="L43" s="6" t="n"/>
-      <c r="M43" s="6" t="n"/>
+      <c r="M43" s="6">
+        <f>IF(C43="","",COUNTA(G43:J43))</f>
+        <v/>
+      </c>
       <c r="N43" s="6">
-        <f>IF(C43="","",COUNTA(G43:J43))</f>
-        <v/>
-      </c>
-      <c r="O43" s="6">
-        <f>IF(C43="","",IF(N43&lt;F43,"SHORT by "&amp;(F43-N43),"")&amp;IF(L43="",IF(N43&lt;F43," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C43="","",IF(M43&lt;F43,"SHORT by "&amp;(F43-M43),"")&amp;IF(G43="",IF(M43&lt;F43," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4632,13 +4586,12 @@
       <c r="J44" s="6" t="n"/>
       <c r="K44" s="6" t="n"/>
       <c r="L44" s="6" t="n"/>
-      <c r="M44" s="6" t="n"/>
+      <c r="M44" s="6">
+        <f>IF(C44="","",COUNTA(G44:J44))</f>
+        <v/>
+      </c>
       <c r="N44" s="6">
-        <f>IF(C44="","",COUNTA(G44:J44))</f>
-        <v/>
-      </c>
-      <c r="O44" s="6">
-        <f>IF(C44="","",IF(N44&lt;F44,"SHORT by "&amp;(F44-N44),"")&amp;IF(L44="",IF(N44&lt;F44," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C44="","",IF(M44&lt;F44,"SHORT by "&amp;(F44-M44),"")&amp;IF(G44="",IF(M44&lt;F44," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4658,13 +4611,12 @@
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="6" t="n"/>
       <c r="L45" s="6" t="n"/>
-      <c r="M45" s="6" t="n"/>
+      <c r="M45" s="6">
+        <f>IF(C45="","",COUNTA(G45:J45))</f>
+        <v/>
+      </c>
       <c r="N45" s="6">
-        <f>IF(C45="","",COUNTA(G45:J45))</f>
-        <v/>
-      </c>
-      <c r="O45" s="6">
-        <f>IF(C45="","",IF(N45&lt;F45,"SHORT by "&amp;(F45-N45),"")&amp;IF(L45="",IF(N45&lt;F45," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C45="","",IF(M45&lt;F45,"SHORT by "&amp;(F45-M45),"")&amp;IF(G45="",IF(M45&lt;F45," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4684,13 +4636,12 @@
       <c r="J46" s="6" t="n"/>
       <c r="K46" s="6" t="n"/>
       <c r="L46" s="6" t="n"/>
-      <c r="M46" s="6" t="n"/>
+      <c r="M46" s="6">
+        <f>IF(C46="","",COUNTA(G46:J46))</f>
+        <v/>
+      </c>
       <c r="N46" s="6">
-        <f>IF(C46="","",COUNTA(G46:J46))</f>
-        <v/>
-      </c>
-      <c r="O46" s="6">
-        <f>IF(C46="","",IF(N46&lt;F46,"SHORT by "&amp;(F46-N46),"")&amp;IF(L46="",IF(N46&lt;F46," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C46="","",IF(M46&lt;F46,"SHORT by "&amp;(F46-M46),"")&amp;IF(G46="",IF(M46&lt;F46," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4710,13 +4661,12 @@
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="6" t="n"/>
       <c r="L47" s="6" t="n"/>
-      <c r="M47" s="6" t="n"/>
+      <c r="M47" s="6">
+        <f>IF(C47="","",COUNTA(G47:J47))</f>
+        <v/>
+      </c>
       <c r="N47" s="6">
-        <f>IF(C47="","",COUNTA(G47:J47))</f>
-        <v/>
-      </c>
-      <c r="O47" s="6">
-        <f>IF(C47="","",IF(N47&lt;F47,"SHORT by "&amp;(F47-N47),"")&amp;IF(L47="",IF(N47&lt;F47," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C47="","",IF(M47&lt;F47,"SHORT by "&amp;(F47-M47),"")&amp;IF(G47="",IF(M47&lt;F47," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4736,13 +4686,12 @@
       <c r="J48" s="6" t="n"/>
       <c r="K48" s="6" t="n"/>
       <c r="L48" s="6" t="n"/>
-      <c r="M48" s="6" t="n"/>
+      <c r="M48" s="6">
+        <f>IF(C48="","",COUNTA(G48:J48))</f>
+        <v/>
+      </c>
       <c r="N48" s="6">
-        <f>IF(C48="","",COUNTA(G48:J48))</f>
-        <v/>
-      </c>
-      <c r="O48" s="6">
-        <f>IF(C48="","",IF(N48&lt;F48,"SHORT by "&amp;(F48-N48),"")&amp;IF(L48="",IF(N48&lt;F48," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C48="","",IF(M48&lt;F48,"SHORT by "&amp;(F48-M48),"")&amp;IF(G48="",IF(M48&lt;F48," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4762,13 +4711,12 @@
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="6" t="n"/>
       <c r="L49" s="6" t="n"/>
-      <c r="M49" s="6" t="n"/>
+      <c r="M49" s="6">
+        <f>IF(C49="","",COUNTA(G49:J49))</f>
+        <v/>
+      </c>
       <c r="N49" s="6">
-        <f>IF(C49="","",COUNTA(G49:J49))</f>
-        <v/>
-      </c>
-      <c r="O49" s="6">
-        <f>IF(C49="","",IF(N49&lt;F49,"SHORT by "&amp;(F49-N49),"")&amp;IF(L49="",IF(N49&lt;F49," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C49="","",IF(M49&lt;F49,"SHORT by "&amp;(F49-M49),"")&amp;IF(G49="",IF(M49&lt;F49," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4788,13 +4736,12 @@
       <c r="J50" s="6" t="n"/>
       <c r="K50" s="6" t="n"/>
       <c r="L50" s="6" t="n"/>
-      <c r="M50" s="6" t="n"/>
+      <c r="M50" s="6">
+        <f>IF(C50="","",COUNTA(G50:J50))</f>
+        <v/>
+      </c>
       <c r="N50" s="6">
-        <f>IF(C50="","",COUNTA(G50:J50))</f>
-        <v/>
-      </c>
-      <c r="O50" s="6">
-        <f>IF(C50="","",IF(N50&lt;F50,"SHORT by "&amp;(F50-N50),"")&amp;IF(L50="",IF(N50&lt;F50," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C50="","",IF(M50&lt;F50,"SHORT by "&amp;(F50-M50),"")&amp;IF(G50="",IF(M50&lt;F50," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4814,13 +4761,12 @@
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="6" t="n"/>
       <c r="L51" s="6" t="n"/>
-      <c r="M51" s="6" t="n"/>
+      <c r="M51" s="6">
+        <f>IF(C51="","",COUNTA(G51:J51))</f>
+        <v/>
+      </c>
       <c r="N51" s="6">
-        <f>IF(C51="","",COUNTA(G51:J51))</f>
-        <v/>
-      </c>
-      <c r="O51" s="6">
-        <f>IF(C51="","",IF(N51&lt;F51,"SHORT by "&amp;(F51-N51),"")&amp;IF(L51="",IF(N51&lt;F51," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C51="","",IF(M51&lt;F51,"SHORT by "&amp;(F51-M51),"")&amp;IF(G51="",IF(M51&lt;F51," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4840,13 +4786,12 @@
       <c r="J52" s="6" t="n"/>
       <c r="K52" s="6" t="n"/>
       <c r="L52" s="6" t="n"/>
-      <c r="M52" s="6" t="n"/>
+      <c r="M52" s="6">
+        <f>IF(C52="","",COUNTA(G52:J52))</f>
+        <v/>
+      </c>
       <c r="N52" s="6">
-        <f>IF(C52="","",COUNTA(G52:J52))</f>
-        <v/>
-      </c>
-      <c r="O52" s="6">
-        <f>IF(C52="","",IF(N52&lt;F52,"SHORT by "&amp;(F52-N52),"")&amp;IF(L52="",IF(N52&lt;F52," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C52="","",IF(M52&lt;F52,"SHORT by "&amp;(F52-M52),"")&amp;IF(G52="",IF(M52&lt;F52," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4866,13 +4811,12 @@
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="6" t="n"/>
       <c r="L53" s="6" t="n"/>
-      <c r="M53" s="6" t="n"/>
+      <c r="M53" s="6">
+        <f>IF(C53="","",COUNTA(G53:J53))</f>
+        <v/>
+      </c>
       <c r="N53" s="6">
-        <f>IF(C53="","",COUNTA(G53:J53))</f>
-        <v/>
-      </c>
-      <c r="O53" s="6">
-        <f>IF(C53="","",IF(N53&lt;F53,"SHORT by "&amp;(F53-N53),"")&amp;IF(L53="",IF(N53&lt;F53," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C53="","",IF(M53&lt;F53,"SHORT by "&amp;(F53-M53),"")&amp;IF(G53="",IF(M53&lt;F53," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4892,13 +4836,12 @@
       <c r="J54" s="6" t="n"/>
       <c r="K54" s="6" t="n"/>
       <c r="L54" s="6" t="n"/>
-      <c r="M54" s="6" t="n"/>
+      <c r="M54" s="6">
+        <f>IF(C54="","",COUNTA(G54:J54))</f>
+        <v/>
+      </c>
       <c r="N54" s="6">
-        <f>IF(C54="","",COUNTA(G54:J54))</f>
-        <v/>
-      </c>
-      <c r="O54" s="6">
-        <f>IF(C54="","",IF(N54&lt;F54,"SHORT by "&amp;(F54-N54),"")&amp;IF(L54="",IF(N54&lt;F54," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C54="","",IF(M54&lt;F54,"SHORT by "&amp;(F54-M54),"")&amp;IF(G54="",IF(M54&lt;F54," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4918,13 +4861,12 @@
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="6" t="n"/>
       <c r="L55" s="6" t="n"/>
-      <c r="M55" s="6" t="n"/>
+      <c r="M55" s="6">
+        <f>IF(C55="","",COUNTA(G55:J55))</f>
+        <v/>
+      </c>
       <c r="N55" s="6">
-        <f>IF(C55="","",COUNTA(G55:J55))</f>
-        <v/>
-      </c>
-      <c r="O55" s="6">
-        <f>IF(C55="","",IF(N55&lt;F55,"SHORT by "&amp;(F55-N55),"")&amp;IF(L55="",IF(N55&lt;F55," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C55="","",IF(M55&lt;F55,"SHORT by "&amp;(F55-M55),"")&amp;IF(G55="",IF(M55&lt;F55," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4944,13 +4886,12 @@
       <c r="J56" s="6" t="n"/>
       <c r="K56" s="6" t="n"/>
       <c r="L56" s="6" t="n"/>
-      <c r="M56" s="6" t="n"/>
+      <c r="M56" s="6">
+        <f>IF(C56="","",COUNTA(G56:J56))</f>
+        <v/>
+      </c>
       <c r="N56" s="6">
-        <f>IF(C56="","",COUNTA(G56:J56))</f>
-        <v/>
-      </c>
-      <c r="O56" s="6">
-        <f>IF(C56="","",IF(N56&lt;F56,"SHORT by "&amp;(F56-N56),"")&amp;IF(L56="",IF(N56&lt;F56," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C56="","",IF(M56&lt;F56,"SHORT by "&amp;(F56-M56),"")&amp;IF(G56="",IF(M56&lt;F56," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4970,13 +4911,12 @@
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="6" t="n"/>
       <c r="L57" s="6" t="n"/>
-      <c r="M57" s="6" t="n"/>
+      <c r="M57" s="6">
+        <f>IF(C57="","",COUNTA(G57:J57))</f>
+        <v/>
+      </c>
       <c r="N57" s="6">
-        <f>IF(C57="","",COUNTA(G57:J57))</f>
-        <v/>
-      </c>
-      <c r="O57" s="6">
-        <f>IF(C57="","",IF(N57&lt;F57,"SHORT by "&amp;(F57-N57),"")&amp;IF(L57="",IF(N57&lt;F57," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C57="","",IF(M57&lt;F57,"SHORT by "&amp;(F57-M57),"")&amp;IF(G57="",IF(M57&lt;F57," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -4996,13 +4936,12 @@
       <c r="J58" s="6" t="n"/>
       <c r="K58" s="6" t="n"/>
       <c r="L58" s="6" t="n"/>
-      <c r="M58" s="6" t="n"/>
+      <c r="M58" s="6">
+        <f>IF(C58="","",COUNTA(G58:J58))</f>
+        <v/>
+      </c>
       <c r="N58" s="6">
-        <f>IF(C58="","",COUNTA(G58:J58))</f>
-        <v/>
-      </c>
-      <c r="O58" s="6">
-        <f>IF(C58="","",IF(N58&lt;F58,"SHORT by "&amp;(F58-N58),"")&amp;IF(L58="",IF(N58&lt;F58," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C58="","",IF(M58&lt;F58,"SHORT by "&amp;(F58-M58),"")&amp;IF(G58="",IF(M58&lt;F58," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5022,13 +4961,12 @@
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="6" t="n"/>
       <c r="L59" s="6" t="n"/>
-      <c r="M59" s="6" t="n"/>
+      <c r="M59" s="6">
+        <f>IF(C59="","",COUNTA(G59:J59))</f>
+        <v/>
+      </c>
       <c r="N59" s="6">
-        <f>IF(C59="","",COUNTA(G59:J59))</f>
-        <v/>
-      </c>
-      <c r="O59" s="6">
-        <f>IF(C59="","",IF(N59&lt;F59,"SHORT by "&amp;(F59-N59),"")&amp;IF(L59="",IF(N59&lt;F59," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C59="","",IF(M59&lt;F59,"SHORT by "&amp;(F59-M59),"")&amp;IF(G59="",IF(M59&lt;F59," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5048,13 +4986,12 @@
       <c r="J60" s="6" t="n"/>
       <c r="K60" s="6" t="n"/>
       <c r="L60" s="6" t="n"/>
-      <c r="M60" s="6" t="n"/>
+      <c r="M60" s="6">
+        <f>IF(C60="","",COUNTA(G60:J60))</f>
+        <v/>
+      </c>
       <c r="N60" s="6">
-        <f>IF(C60="","",COUNTA(G60:J60))</f>
-        <v/>
-      </c>
-      <c r="O60" s="6">
-        <f>IF(C60="","",IF(N60&lt;F60,"SHORT by "&amp;(F60-N60),"")&amp;IF(L60="",IF(N60&lt;F60," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C60="","",IF(M60&lt;F60,"SHORT by "&amp;(F60-M60),"")&amp;IF(G60="",IF(M60&lt;F60," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5074,13 +5011,12 @@
       <c r="J61" s="6" t="n"/>
       <c r="K61" s="6" t="n"/>
       <c r="L61" s="6" t="n"/>
-      <c r="M61" s="6" t="n"/>
+      <c r="M61" s="6">
+        <f>IF(C61="","",COUNTA(G61:J61))</f>
+        <v/>
+      </c>
       <c r="N61" s="6">
-        <f>IF(C61="","",COUNTA(G61:J61))</f>
-        <v/>
-      </c>
-      <c r="O61" s="6">
-        <f>IF(C61="","",IF(N61&lt;F61,"SHORT by "&amp;(F61-N61),"")&amp;IF(L61="",IF(N61&lt;F61," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C61="","",IF(M61&lt;F61,"SHORT by "&amp;(F61-M61),"")&amp;IF(G61="",IF(M61&lt;F61," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5100,13 +5036,12 @@
       <c r="J62" s="6" t="n"/>
       <c r="K62" s="6" t="n"/>
       <c r="L62" s="6" t="n"/>
-      <c r="M62" s="6" t="n"/>
+      <c r="M62" s="6">
+        <f>IF(C62="","",COUNTA(G62:J62))</f>
+        <v/>
+      </c>
       <c r="N62" s="6">
-        <f>IF(C62="","",COUNTA(G62:J62))</f>
-        <v/>
-      </c>
-      <c r="O62" s="6">
-        <f>IF(C62="","",IF(N62&lt;F62,"SHORT by "&amp;(F62-N62),"")&amp;IF(L62="",IF(N62&lt;F62," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C62="","",IF(M62&lt;F62,"SHORT by "&amp;(F62-M62),"")&amp;IF(G62="",IF(M62&lt;F62," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5126,13 +5061,12 @@
       <c r="J63" s="6" t="n"/>
       <c r="K63" s="6" t="n"/>
       <c r="L63" s="6" t="n"/>
-      <c r="M63" s="6" t="n"/>
+      <c r="M63" s="6">
+        <f>IF(C63="","",COUNTA(G63:J63))</f>
+        <v/>
+      </c>
       <c r="N63" s="6">
-        <f>IF(C63="","",COUNTA(G63:J63))</f>
-        <v/>
-      </c>
-      <c r="O63" s="6">
-        <f>IF(C63="","",IF(N63&lt;F63,"SHORT by "&amp;(F63-N63),"")&amp;IF(L63="",IF(N63&lt;F63," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C63="","",IF(M63&lt;F63,"SHORT by "&amp;(F63-M63),"")&amp;IF(G63="",IF(M63&lt;F63," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5152,13 +5086,12 @@
       <c r="J64" s="6" t="n"/>
       <c r="K64" s="6" t="n"/>
       <c r="L64" s="6" t="n"/>
-      <c r="M64" s="6" t="n"/>
+      <c r="M64" s="6">
+        <f>IF(C64="","",COUNTA(G64:J64))</f>
+        <v/>
+      </c>
       <c r="N64" s="6">
-        <f>IF(C64="","",COUNTA(G64:J64))</f>
-        <v/>
-      </c>
-      <c r="O64" s="6">
-        <f>IF(C64="","",IF(N64&lt;F64,"SHORT by "&amp;(F64-N64),"")&amp;IF(L64="",IF(N64&lt;F64," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C64="","",IF(M64&lt;F64,"SHORT by "&amp;(F64-M64),"")&amp;IF(G64="",IF(M64&lt;F64," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5178,13 +5111,12 @@
       <c r="J65" s="6" t="n"/>
       <c r="K65" s="6" t="n"/>
       <c r="L65" s="6" t="n"/>
-      <c r="M65" s="6" t="n"/>
+      <c r="M65" s="6">
+        <f>IF(C65="","",COUNTA(G65:J65))</f>
+        <v/>
+      </c>
       <c r="N65" s="6">
-        <f>IF(C65="","",COUNTA(G65:J65))</f>
-        <v/>
-      </c>
-      <c r="O65" s="6">
-        <f>IF(C65="","",IF(N65&lt;F65,"SHORT by "&amp;(F65-N65),"")&amp;IF(L65="",IF(N65&lt;F65," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C65="","",IF(M65&lt;F65,"SHORT by "&amp;(F65-M65),"")&amp;IF(G65="",IF(M65&lt;F65," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5204,13 +5136,12 @@
       <c r="J66" s="6" t="n"/>
       <c r="K66" s="6" t="n"/>
       <c r="L66" s="6" t="n"/>
-      <c r="M66" s="6" t="n"/>
+      <c r="M66" s="6">
+        <f>IF(C66="","",COUNTA(G66:J66))</f>
+        <v/>
+      </c>
       <c r="N66" s="6">
-        <f>IF(C66="","",COUNTA(G66:J66))</f>
-        <v/>
-      </c>
-      <c r="O66" s="6">
-        <f>IF(C66="","",IF(N66&lt;F66,"SHORT by "&amp;(F66-N66),"")&amp;IF(L66="",IF(N66&lt;F66," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C66="","",IF(M66&lt;F66,"SHORT by "&amp;(F66-M66),"")&amp;IF(G66="",IF(M66&lt;F66," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5230,13 +5161,12 @@
       <c r="J67" s="6" t="n"/>
       <c r="K67" s="6" t="n"/>
       <c r="L67" s="6" t="n"/>
-      <c r="M67" s="6" t="n"/>
+      <c r="M67" s="6">
+        <f>IF(C67="","",COUNTA(G67:J67))</f>
+        <v/>
+      </c>
       <c r="N67" s="6">
-        <f>IF(C67="","",COUNTA(G67:J67))</f>
-        <v/>
-      </c>
-      <c r="O67" s="6">
-        <f>IF(C67="","",IF(N67&lt;F67,"SHORT by "&amp;(F67-N67),"")&amp;IF(L67="",IF(N67&lt;F67," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C67="","",IF(M67&lt;F67,"SHORT by "&amp;(F67-M67),"")&amp;IF(G67="",IF(M67&lt;F67," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5256,13 +5186,12 @@
       <c r="J68" s="6" t="n"/>
       <c r="K68" s="6" t="n"/>
       <c r="L68" s="6" t="n"/>
-      <c r="M68" s="6" t="n"/>
+      <c r="M68" s="6">
+        <f>IF(C68="","",COUNTA(G68:J68))</f>
+        <v/>
+      </c>
       <c r="N68" s="6">
-        <f>IF(C68="","",COUNTA(G68:J68))</f>
-        <v/>
-      </c>
-      <c r="O68" s="6">
-        <f>IF(C68="","",IF(N68&lt;F68,"SHORT by "&amp;(F68-N68),"")&amp;IF(L68="",IF(N68&lt;F68," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C68="","",IF(M68&lt;F68,"SHORT by "&amp;(F68-M68),"")&amp;IF(G68="",IF(M68&lt;F68," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5282,13 +5211,12 @@
       <c r="J69" s="6" t="n"/>
       <c r="K69" s="6" t="n"/>
       <c r="L69" s="6" t="n"/>
-      <c r="M69" s="6" t="n"/>
+      <c r="M69" s="6">
+        <f>IF(C69="","",COUNTA(G69:J69))</f>
+        <v/>
+      </c>
       <c r="N69" s="6">
-        <f>IF(C69="","",COUNTA(G69:J69))</f>
-        <v/>
-      </c>
-      <c r="O69" s="6">
-        <f>IF(C69="","",IF(N69&lt;F69,"SHORT by "&amp;(F69-N69),"")&amp;IF(L69="",IF(N69&lt;F69," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C69="","",IF(M69&lt;F69,"SHORT by "&amp;(F69-M69),"")&amp;IF(G69="",IF(M69&lt;F69," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5308,13 +5236,12 @@
       <c r="J70" s="6" t="n"/>
       <c r="K70" s="6" t="n"/>
       <c r="L70" s="6" t="n"/>
-      <c r="M70" s="6" t="n"/>
+      <c r="M70" s="6">
+        <f>IF(C70="","",COUNTA(G70:J70))</f>
+        <v/>
+      </c>
       <c r="N70" s="6">
-        <f>IF(C70="","",COUNTA(G70:J70))</f>
-        <v/>
-      </c>
-      <c r="O70" s="6">
-        <f>IF(C70="","",IF(N70&lt;F70,"SHORT by "&amp;(F70-N70),"")&amp;IF(L70="",IF(N70&lt;F70," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C70="","",IF(M70&lt;F70,"SHORT by "&amp;(F70-M70),"")&amp;IF(G70="",IF(M70&lt;F70," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5334,13 +5261,12 @@
       <c r="J71" s="6" t="n"/>
       <c r="K71" s="6" t="n"/>
       <c r="L71" s="6" t="n"/>
-      <c r="M71" s="6" t="n"/>
+      <c r="M71" s="6">
+        <f>IF(C71="","",COUNTA(G71:J71))</f>
+        <v/>
+      </c>
       <c r="N71" s="6">
-        <f>IF(C71="","",COUNTA(G71:J71))</f>
-        <v/>
-      </c>
-      <c r="O71" s="6">
-        <f>IF(C71="","",IF(N71&lt;F71,"SHORT by "&amp;(F71-N71),"")&amp;IF(L71="",IF(N71&lt;F71," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C71="","",IF(M71&lt;F71,"SHORT by "&amp;(F71-M71),"")&amp;IF(G71="",IF(M71&lt;F71," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5360,13 +5286,12 @@
       <c r="J72" s="6" t="n"/>
       <c r="K72" s="6" t="n"/>
       <c r="L72" s="6" t="n"/>
-      <c r="M72" s="6" t="n"/>
+      <c r="M72" s="6">
+        <f>IF(C72="","",COUNTA(G72:J72))</f>
+        <v/>
+      </c>
       <c r="N72" s="6">
-        <f>IF(C72="","",COUNTA(G72:J72))</f>
-        <v/>
-      </c>
-      <c r="O72" s="6">
-        <f>IF(C72="","",IF(N72&lt;F72,"SHORT by "&amp;(F72-N72),"")&amp;IF(L72="",IF(N72&lt;F72," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C72="","",IF(M72&lt;F72,"SHORT by "&amp;(F72-M72),"")&amp;IF(G72="",IF(M72&lt;F72," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5386,13 +5311,12 @@
       <c r="J73" s="6" t="n"/>
       <c r="K73" s="6" t="n"/>
       <c r="L73" s="6" t="n"/>
-      <c r="M73" s="6" t="n"/>
+      <c r="M73" s="6">
+        <f>IF(C73="","",COUNTA(G73:J73))</f>
+        <v/>
+      </c>
       <c r="N73" s="6">
-        <f>IF(C73="","",COUNTA(G73:J73))</f>
-        <v/>
-      </c>
-      <c r="O73" s="6">
-        <f>IF(C73="","",IF(N73&lt;F73,"SHORT by "&amp;(F73-N73),"")&amp;IF(L73="",IF(N73&lt;F73," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C73="","",IF(M73&lt;F73,"SHORT by "&amp;(F73-M73),"")&amp;IF(G73="",IF(M73&lt;F73," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5412,13 +5336,12 @@
       <c r="J74" s="6" t="n"/>
       <c r="K74" s="6" t="n"/>
       <c r="L74" s="6" t="n"/>
-      <c r="M74" s="6" t="n"/>
+      <c r="M74" s="6">
+        <f>IF(C74="","",COUNTA(G74:J74))</f>
+        <v/>
+      </c>
       <c r="N74" s="6">
-        <f>IF(C74="","",COUNTA(G74:J74))</f>
-        <v/>
-      </c>
-      <c r="O74" s="6">
-        <f>IF(C74="","",IF(N74&lt;F74,"SHORT by "&amp;(F74-N74),"")&amp;IF(L74="",IF(N74&lt;F74," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C74="","",IF(M74&lt;F74,"SHORT by "&amp;(F74-M74),"")&amp;IF(G74="",IF(M74&lt;F74," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5438,13 +5361,12 @@
       <c r="J75" s="6" t="n"/>
       <c r="K75" s="6" t="n"/>
       <c r="L75" s="6" t="n"/>
-      <c r="M75" s="6" t="n"/>
+      <c r="M75" s="6">
+        <f>IF(C75="","",COUNTA(G75:J75))</f>
+        <v/>
+      </c>
       <c r="N75" s="6">
-        <f>IF(C75="","",COUNTA(G75:J75))</f>
-        <v/>
-      </c>
-      <c r="O75" s="6">
-        <f>IF(C75="","",IF(N75&lt;F75,"SHORT by "&amp;(F75-N75),"")&amp;IF(L75="",IF(N75&lt;F75," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C75="","",IF(M75&lt;F75,"SHORT by "&amp;(F75-M75),"")&amp;IF(G75="",IF(M75&lt;F75," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5464,13 +5386,12 @@
       <c r="J76" s="6" t="n"/>
       <c r="K76" s="6" t="n"/>
       <c r="L76" s="6" t="n"/>
-      <c r="M76" s="6" t="n"/>
+      <c r="M76" s="6">
+        <f>IF(C76="","",COUNTA(G76:J76))</f>
+        <v/>
+      </c>
       <c r="N76" s="6">
-        <f>IF(C76="","",COUNTA(G76:J76))</f>
-        <v/>
-      </c>
-      <c r="O76" s="6">
-        <f>IF(C76="","",IF(N76&lt;F76,"SHORT by "&amp;(F76-N76),"")&amp;IF(L76="",IF(N76&lt;F76," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C76="","",IF(M76&lt;F76,"SHORT by "&amp;(F76-M76),"")&amp;IF(G76="",IF(M76&lt;F76," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5490,13 +5411,12 @@
       <c r="J77" s="6" t="n"/>
       <c r="K77" s="6" t="n"/>
       <c r="L77" s="6" t="n"/>
-      <c r="M77" s="6" t="n"/>
+      <c r="M77" s="6">
+        <f>IF(C77="","",COUNTA(G77:J77))</f>
+        <v/>
+      </c>
       <c r="N77" s="6">
-        <f>IF(C77="","",COUNTA(G77:J77))</f>
-        <v/>
-      </c>
-      <c r="O77" s="6">
-        <f>IF(C77="","",IF(N77&lt;F77,"SHORT by "&amp;(F77-N77),"")&amp;IF(L77="",IF(N77&lt;F77," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C77="","",IF(M77&lt;F77,"SHORT by "&amp;(F77-M77),"")&amp;IF(G77="",IF(M77&lt;F77," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5516,13 +5436,12 @@
       <c r="J78" s="6" t="n"/>
       <c r="K78" s="6" t="n"/>
       <c r="L78" s="6" t="n"/>
-      <c r="M78" s="6" t="n"/>
+      <c r="M78" s="6">
+        <f>IF(C78="","",COUNTA(G78:J78))</f>
+        <v/>
+      </c>
       <c r="N78" s="6">
-        <f>IF(C78="","",COUNTA(G78:J78))</f>
-        <v/>
-      </c>
-      <c r="O78" s="6">
-        <f>IF(C78="","",IF(N78&lt;F78,"SHORT by "&amp;(F78-N78),"")&amp;IF(L78="",IF(N78&lt;F78," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C78="","",IF(M78&lt;F78,"SHORT by "&amp;(F78-M78),"")&amp;IF(G78="",IF(M78&lt;F78," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5542,13 +5461,12 @@
       <c r="J79" s="6" t="n"/>
       <c r="K79" s="6" t="n"/>
       <c r="L79" s="6" t="n"/>
-      <c r="M79" s="6" t="n"/>
+      <c r="M79" s="6">
+        <f>IF(C79="","",COUNTA(G79:J79))</f>
+        <v/>
+      </c>
       <c r="N79" s="6">
-        <f>IF(C79="","",COUNTA(G79:J79))</f>
-        <v/>
-      </c>
-      <c r="O79" s="6">
-        <f>IF(C79="","",IF(N79&lt;F79,"SHORT by "&amp;(F79-N79),"")&amp;IF(L79="",IF(N79&lt;F79," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C79="","",IF(M79&lt;F79,"SHORT by "&amp;(F79-M79),"")&amp;IF(G79="",IF(M79&lt;F79," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
@@ -5568,23 +5486,22 @@
       <c r="J80" s="6" t="n"/>
       <c r="K80" s="6" t="n"/>
       <c r="L80" s="6" t="n"/>
-      <c r="M80" s="6" t="n"/>
+      <c r="M80" s="6">
+        <f>IF(C80="","",COUNTA(G80:J80))</f>
+        <v/>
+      </c>
       <c r="N80" s="6">
-        <f>IF(C80="","",COUNTA(G80:J80))</f>
-        <v/>
-      </c>
-      <c r="O80" s="6">
-        <f>IF(C80="","",IF(N80&lt;F80,"SHORT by "&amp;(F80-N80),"")&amp;IF(L80="",IF(N80&lt;F80," · ","")&amp;"NO SAFETY BOAT DRIVER",""))</f>
+        <f>IF(C80="","",IF(M80&lt;F80,"SHORT by "&amp;(F80-M80),"")&amp;IF(G80="",IF(M80&lt;F80," · ","")&amp;"NO SENIOR INSTRUCTOR",""))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="O2:O80">
+  <conditionalFormatting sqref="N2:N80">
     <cfRule type="expression" priority="1" dxfId="2">
-      <formula>AND(O2&lt;&gt;"",C2&lt;&gt;"")</formula>
+      <formula>AND(N2&lt;&gt;"",C2&lt;&gt;"")</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="3">
-      <formula>AND(O2="",C2&lt;&gt;"")</formula>
+      <formula>AND(N2="",C2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
